--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -773,7 +773,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -952,7 +952,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Teemu Roos</t>
+          <t>Jukka Talvitie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,7 +968,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>machine learning &amp; algorithms</t>
+          <t>Toward Seamless Localization: Situational Awareness Using UWB Wearable Systems and Convolutional Neural Networks (2023)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -982,18 +982,22 @@
       <c r="J12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044609448</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luca Benini </t>
+          <t>Luca Benini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,7 +1013,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>include energy-efficient computing systems, embedded systems, machine learning hardware</t>
+          <t>Self-Sustaining Ultrawideband Positioning System for Event-Driven Indoor Localization (2023)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1023,18 +1027,22 @@
       <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043408422</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tulika Mitra</t>
+          <t>Cheng‐Wei Qiu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1050,7 +1058,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>“low-power reconfigurable edge accelerators”, “embedded systems”, “application-specific processors”</t>
+          <t>Origami metamaterials for ultra-wideband and large-depth reflection modulation (2024)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1064,18 +1072,22 @@
       <c r="J14" t="n">
         <v>10</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089609880</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nikil Dutt</t>
+          <t>Solmaz S. Kia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1091,7 +1103,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>embedded systems, electronic design automation, computer architecture, hardware/software co‐design</t>
+          <t>Self-Localizing On-Demand Portable Wireless Beacons for Coverage Enhancement of RF Beacon-Based Indoor Localization Systems (2023)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1105,11 +1117,15 @@
       <c r="J15" t="n">
         <v>8</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049439078</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1149,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cheng‐Wei Qiu</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>National University of Singapore (NUS)</t>
@@ -1145,7 +1165,11 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Origami metamaterials for ultra-wideband and large-depth reflection modulation (2024)</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1153,11 +1177,15 @@
       <c r="J17" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089609880</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1214,12 +1214,16 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cheng‐Wei Qiu</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Singapore University of Technology and Design (QS 519)</t>
@@ -1231,7 +1235,11 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Origami metamaterials for ultra-wideband and large-depth reflection modulation (2024)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1241,13 +1249,13 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>I like it</t>
+          <t>https://openalex.org/A5089609880</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1284,16 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sarah Whitehead</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>University of Otago</t>
@@ -1293,7 +1305,11 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Consensus on a netball video analysis framework of descriptors and definitions by the netball video analysis consensus group (2023)</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1301,16 +1317,24 @@
       <c r="J21" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045152528</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Xuan Song</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>The University of Tokyo</t>
@@ -1322,7 +1346,11 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Domain Adversarial Graph Convolutional Network Based on RSSI and Crowdsensing for Indoor Localization (2023)</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -1330,11 +1358,15 @@
       <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046856721</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1371,7 +1371,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hiroshi Harada</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Kyoto University</t>
@@ -1383,7 +1387,11 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3GPP-Compatible Channel Generation Framework for FR2-2 Indoor Short-Range Communication (2023)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1391,16 +1399,24 @@
       <c r="J23" t="n">
         <v>10</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087987207</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Yi‐Ping Hung</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Tokyo Institute of Technology (Tokyo Tech)</t>
@@ -1412,7 +1428,11 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VIUNet: Deep Visual–Inertial–UWB Fusion for Indoor UAV Localization (2023)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1420,16 +1440,24 @@
       <c r="J24" t="n">
         <v>10</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5102935450</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Moustafa Youssef</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Osaka University</t>
@@ -1441,7 +1469,11 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Privacy-Preserving by Design: Indoor Positioning System Using Wi-Fi Passive TDOA (2023)</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1449,16 +1481,24 @@
       <c r="J25" t="n">
         <v>10</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5008352007</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shinichiro Omachi</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Tohoku University</t>
@@ -1470,7 +1510,11 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Collaborative Indoor Positioning by Localization Comparison at an Encounter Position (2023)</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1478,16 +1522,24 @@
       <c r="J26" t="n">
         <v>9</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020830042</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nobuo Kawaguchi</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Nagoya University</t>
@@ -1499,7 +1551,11 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>A Survey of Ground Truth Measurement Systems for Indoor Positioning (2023)</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1507,11 +1563,15 @@
       <c r="J27" t="n">
         <v>9</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5045353484</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1576,7 +1576,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hiromichi Hashizume</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Hokkaido University</t>
@@ -1588,7 +1592,11 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Smartphone Indoor Positioning using Inertial and Ambient Light Sensors (2023)</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1596,16 +1604,24 @@
       <c r="J28" t="n">
         <v>9</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5102856248</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ryo Kurazume</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Kyushu University</t>
@@ -1617,7 +1633,11 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Indoor Position Estimation using NLoS Information by Wireless Distance Sensors (2023)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1625,16 +1645,24 @@
       <c r="J29" t="n">
         <v>9</v>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073445963</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Siti Rohana Ahmad Ibrahim</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Waseda University</t>
@@ -1646,7 +1674,11 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A Review of Indoor Positioning Systems for UAV Localization with Machine Learning Algorithms (2023)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1654,16 +1686,24 @@
       <c r="J30" t="n">
         <v>9</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020400844</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guan Gui</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Keio University</t>
@@ -1675,7 +1715,11 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Regularized Multi-Label Learning Empowered Joint Activity Recognition and Indoor Localization With CSI Fingerprints (2024)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1683,16 +1727,24 @@
       <c r="J31" t="n">
         <v>9</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5027367677</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Donghwan Lee</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Seoul National University</t>
@@ -1704,7 +1756,11 @@
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WayIL: Image-based Indoor Localization with Wayfinding Maps (2024)</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -1712,11 +1768,15 @@
       <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100654317</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1781,7 +1781,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jiwon Seo</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Yonsei University</t>
@@ -1793,7 +1797,11 @@
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Low-Cost GNSS Simulators With Wireless Clock Synchronization for Indoor Positioning (2023)</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1801,16 +1809,24 @@
       <c r="J33" t="n">
         <v>10</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100657256</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Wonjae Shin</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Korea University</t>
@@ -1822,7 +1838,11 @@
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Toward Integrated Sensing and Communications for 6G: Key Enabling Technologies, Standardization, and Challenges (2024)</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1830,16 +1850,24 @@
       <c r="J34" t="n">
         <v>10</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009725517</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kyung‐Tae Kim</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Pohang University of Science And Technology (POSTECH)</t>
@@ -1851,7 +1879,11 @@
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Multipath Signal Mitigation for Indoor Localization Based on MIMO FMCW Radar System (2023)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1859,16 +1891,24 @@
       <c r="J35" t="n">
         <v>10</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100713090</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Daehan Kwak</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Sungkyunkwan University (SKKU)</t>
@@ -1880,7 +1920,11 @@
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>A Systematic Review of Contemporary Indoor Positioning Systems: Taxonomy, Techniques, and Algorithms (2024)</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1888,16 +1932,24 @@
       <c r="J36" t="n">
         <v>10</v>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009184228</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jae-il Jung</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Hanyang University</t>
@@ -1909,7 +1961,11 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Accurate Indoor Positioning for UWB-Based Personal Devices Using Deep Learning (2023)</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1917,11 +1973,15 @@
       <c r="J37" t="n">
         <v>9</v>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081367261</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1986,7 +1986,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Gangil Byun</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Ulsan National Institute of Science and Technology (UNIST)</t>
@@ -1998,7 +2002,11 @@
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ultra-Wideband Frequency-Invariant Beamforming Using a Generalized Nesting Array (2024)</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -2006,16 +2014,24 @@
       <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044783058</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Joongeup Kye</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Kyung Hee University</t>
@@ -2027,7 +2043,11 @@
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Comparative Analysis of Integrated Filtering Methods Using UWB Localization in Indoor Environment (2024)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -2035,16 +2055,24 @@
       <c r="J39" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080533010</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>X. J. Zhu</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Beijing Normal University</t>
@@ -2056,7 +2084,11 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ultra-wideband polarimetry of the April 2021 profile change event in PSR J1713+0747 (2025)</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -2064,16 +2096,24 @@
       <c r="J40" t="n">
         <v>7</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033053320</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Xingjun Wang</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Peking University</t>
@@ -2085,7 +2125,11 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Integrated photonics enabling ultra-wideband fibre–wireless communication (2026)</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -2093,16 +2137,24 @@
       <c r="J41" t="n">
         <v>10</v>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5126346057</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Zheng Yang</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tsinghua University</t>
@@ -2114,7 +2166,11 @@
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>REFLoc: A Resilient Evolutionary Fusion Framework for Robust Indoor Localization (2024)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -2122,11 +2178,15 @@
       <c r="J42" t="n">
         <v>10</v>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061103594</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2191,7 +2191,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Xin Wang</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Fudan University</t>
@@ -2203,7 +2207,11 @@
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>A Survey of Latest Wi-Fi Assisted Indoor Positioning on Different Principles (2023)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -2211,16 +2219,24 @@
       <c r="J43" t="n">
         <v>10</v>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5061028507</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Yikai Su</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Shanghai Jiao Tong University</t>
@@ -2232,7 +2248,11 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ultra‐wideband integrated photonic devices on silicon platform: from visible to mid‐IR (2023)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -2240,16 +2260,24 @@
       <c r="J44" t="n">
         <v>10</v>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026515323</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tong Cai</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Zhejiang University</t>
@@ -2261,7 +2289,11 @@
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Multi-characteristic Integrated Ultra-wideband Frequency Selective Rasorber (2024)</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -2269,16 +2301,24 @@
       <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5110977361</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Junming Zhao</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Nanjing University</t>
@@ -2290,7 +2330,11 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>A Novel Ultra‐Wideband Electromagnetic‐Wave‐Absorbing Metastructure Inspired by Bionic Gyroid Structures (2023)</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -2298,16 +2342,24 @@
       <c r="J46" t="n">
         <v>10</v>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024794935</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Yikai Su</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Shanghai Jiao Tong University</t>
@@ -2319,7 +2371,11 @@
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ultra‐wideband integrated photonic devices on silicon platform: from visible to mid‐IR (2023)</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -2327,11 +2383,15 @@
       <c r="J47" t="n">
         <v>10</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026515323</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2396,7 +2396,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Yuanming Shi</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Zhejiang University</t>
@@ -2408,7 +2412,11 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Energy-Efficient Optimal Mode Selection for Edge AI Inference via Integrated Sensing-Communication-Computation (2024)</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -2416,11 +2424,15 @@
       <c r="J48" t="n">
         <v>10</v>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5022499594</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2461,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2490,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2519,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2548,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2553,7 +2553,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Lars Rönnegård</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>University of Copenhagen</t>
@@ -2565,7 +2569,11 @@
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cow characteristics associated with the variation in number of contacts between dairy cows (2023)</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -2573,16 +2581,24 @@
       <c r="J53" t="n">
         <v>10</v>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5085747746</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Xiaolong Zhu</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Technical University of Denmark</t>
@@ -2594,7 +2610,11 @@
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Application of metasurface in future displays (2025)</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -2602,16 +2622,24 @@
       <c r="J54" t="n">
         <v>10</v>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5072550494</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Markus Münzenberg</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Aarhus University</t>
@@ -2623,7 +2651,11 @@
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Comparative analysis of THz signal emission from bilayer heterostructures: Wideband and high-frequency THz signal advantage of PtBi-based emitter (2024)</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -2631,16 +2663,24 @@
       <c r="J55" t="n">
         <v>10</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089808777</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Susana Póvoas</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>University of Southern Denmark (SDU)</t>
@@ -2652,7 +2692,11 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Positional differences in match performance for key elite male team handball players at the EHF EURO 2022 (2026)</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -2660,16 +2704,24 @@
       <c r="J56" t="n">
         <v>8</v>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080521951</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Yang Miao</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Aalborg University</t>
@@ -2681,7 +2733,11 @@
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>A UAV-Aided Real-Time Channel Sounder for Highly Dynamic Nonstationary A2G Scenarios (2023)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -2689,11 +2745,15 @@
       <c r="J57" t="n">
         <v>8</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039982512</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2758,7 +2758,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ingve Simonsen</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Norwegian University of Science And Technology</t>
@@ -2770,7 +2774,11 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Switchable Ultra-Wideband All-Optical Quantum Dot Reflective Semiconductor Optical Amplifier (2023)</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -2778,16 +2786,24 @@
       <c r="J58" t="n">
         <v>8</v>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5037337156</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Henrik Baktoft</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>University of Bergen</t>
@@ -2799,7 +2815,11 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Positioning aquatic animals with acoustic transmitters (2023)</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -2807,16 +2827,24 @@
       <c r="J59" t="n">
         <v>8</v>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087753687</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nobby Stevens</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>KU Leuven</t>
@@ -2828,7 +2856,11 @@
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>An Experimental Testbed for the Performance Evaluation of Optical Time Difference of Arrival Based Indoor Positioning (2024)</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -2836,16 +2868,24 @@
       <c r="J60" t="n">
         <v>10</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020679063</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Eli De Poorter</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Ghent University</t>
@@ -2857,7 +2897,11 @@
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ultra Wideband (UWB) Localization Using Active CIR-Based Fingerprinting (2023)</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -2865,16 +2909,24 @@
       <c r="J61" t="n">
         <v>9</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5026442244</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Radu-Daniel Vatavu</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Université catholique de Louvain (UCLouvain)</t>
@@ -2886,7 +2938,11 @@
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RadarSense: Accurate Recognition of Mid-air Hand Gestures with Radar Sensing and Few Training Examples (2023)</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -2894,11 +2950,15 @@
       <c r="J62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5033726877</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2987,12 +2987,16 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Orhan Dağdevıren</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>University of Antwerp</t>
@@ -3004,7 +3008,11 @@
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>An Experimental Evaluation of Indoor Localization in Autonomous Mobile Robots (2025)</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
@@ -3012,16 +3020,24 @@
       <c r="J64" t="n">
         <v>10</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004224779</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Johan Stien</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Vrije Universiteit Brussel (VUB)</t>
@@ -3033,7 +3049,11 @@
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Machine learning-optimized terahertz ultra-wideband tunable metamaterial absorber (2025)</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -3041,16 +3061,24 @@
       <c r="J65" t="n">
         <v>8</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5117422059</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Emily Arnold</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Université de Liège</t>
@@ -3062,7 +3090,11 @@
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Snow stratigraphy observations from Operation IceBridge surveys in Alaska using S and C band airborne ultra-wideband FMCW (frequency-modulated continuous wave) radar (2023)</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
@@ -3070,16 +3102,24 @@
       <c r="J66" t="n">
         <v>7</v>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5000544440</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Fredrik Tufvesson</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Lund University</t>
@@ -3091,7 +3131,11 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>High-Precision Machine-Learning Based Indoor Localization with Massive MIMO System (2023)</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -3099,11 +3143,15 @@
       <c r="J67" t="n">
         <v>10</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5073439066</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3156,7 +3156,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mikael Gidlund</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>KTH Royal Institute of Technology</t>
@@ -3168,7 +3172,11 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Indoor Positioning in 5G-Advanced: Challenges and Solution Toward Centimeter-Level Accuracy with Carrier Phase Enhancements (2024)</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
@@ -3176,16 +3184,24 @@
       <c r="J68" t="n">
         <v>10</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004012289</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Isaac Skog</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Uppsala University</t>
@@ -3197,7 +3213,11 @@
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MAINS: A Magnetic Field Aided Inertial Navigation System for Indoor Positioning (2023)</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -3205,16 +3225,24 @@
       <c r="J69" t="n">
         <v>10</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057769293</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Henrik Baktoft</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Stockholm University</t>
@@ -3226,7 +3254,11 @@
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Positioning aquatic animals with acoustic transmitters (2023)</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -3234,16 +3266,24 @@
       <c r="J70" t="n">
         <v>9</v>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5087753687</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mikko Valkama</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Chalmers University of Technology</t>
@@ -3255,7 +3295,11 @@
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Failure Tolerant Phase-Only Indoor Positioning via Deep Learning (2025)</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -3263,16 +3307,24 @@
       <c r="J71" t="n">
         <v>9</v>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054197935</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Daniel Arvidsson</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>University of Gothenburg</t>
@@ -3284,7 +3336,11 @@
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fourteen days free-living evaluation of an open-source algorithm for counting steps in healthy adults with a large variation in physical activity level (2023)</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -3292,11 +3348,15 @@
       <c r="J72" t="n">
         <v>8</v>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078102195</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3361,7 +3361,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Daniel Arvidsson</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>University of Gothenburg</t>
@@ -3373,7 +3377,11 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fourteen days free-living evaluation of an open-source algorithm for counting steps in healthy adults with a large variation in physical activity level (2023)</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
@@ -3381,11 +3389,15 @@
       <c r="J73" t="n">
         <v>7</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078102195</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3426,16 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nuria González‐Prelcic</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Aalto University</t>
@@ -3431,7 +3447,11 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Multicarrier ISAC: Advances in waveform design, signal processing, and learning under nonidealities (2024)</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -3439,16 +3459,24 @@
       <c r="J75" t="n">
         <v>9</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056278281</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jukka Talvitie</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>University of Helsinki</t>
@@ -3460,7 +3488,11 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Toward Seamless Localization: Situational Awareness Using UWB Wearable Systems and Convolutional Neural Networks (2023)</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
@@ -3468,16 +3500,24 @@
       <c r="J76" t="n">
         <v>9</v>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5044609448</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Markku Juntti</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>University of Oulu</t>
@@ -3491,7 +3531,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>very good for wireless/uwb/6g</t>
+          <t>Performance Analysis and Power Allocation for Massive MIMO ISAC Systems (2025)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3501,11 +3541,15 @@
       <c r="J77" t="n">
         <v>7</v>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5029534229</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3554,7 +3554,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jorge Peña-Queralta</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>University of Turku</t>
@@ -3566,7 +3570,11 @@
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Exploiting redundancy for UWB anomaly detection in infrastructure-free multi-robot relative localization (2023)</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
@@ -3574,16 +3582,24 @@
       <c r="J78" t="n">
         <v>7</v>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5093561961</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zhen Zhang</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Lappeenranta-Lahti University of Technology LUT</t>
@@ -3595,7 +3611,11 @@
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Research on 3D Localization Technology Based on Hybrid Signal Models and Adaptive Dynamic Weight Whale Optimization Algorithm (2025)</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
@@ -3603,16 +3623,24 @@
       <c r="J79" t="n">
         <v>6</v>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5101480038</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Angela P. Schoellig</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Technical University of Munich</t>
@@ -3626,7 +3654,11 @@
       <c r="D80" t="n">
         <v>22</v>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>UTIL: An ultra-wideband time-difference-of-arrival indoor localization dataset (2024)</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -3634,16 +3666,24 @@
       <c r="J80" t="n">
         <v>10</v>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052147335</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hélène Seroussi</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Ludwig-Maximilians-Universität München</t>
@@ -3657,7 +3697,11 @@
       <c r="D81" t="n">
         <v>58</v>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Heterogeneous Basal Thermal Conditions Underpinning the Adélie‐George V Coast, East Antarctica (2024)</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
@@ -3665,16 +3709,24 @@
       <c r="J81" t="n">
         <v>9</v>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046027378</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jari Nurmi</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Universität Heidelberg</t>
@@ -3688,7 +3740,11 @@
       <c r="D82" t="n">
         <v>80</v>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Adaptive approximate computing in edge AI and IoT applications: A review (2024)</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -3696,11 +3752,15 @@
       <c r="J82" t="n">
         <v>9</v>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5035297149</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3791,12 +3791,16 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Uwe D. Hanebeck</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>KIT, Karlsruhe Institute of Technology</t>
@@ -3810,7 +3814,11 @@
       <c r="D84" t="n">
         <v>98</v>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Continuous-Time Ultra-Wideband-Inertial Fusion (2023)</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -3818,16 +3826,24 @@
       <c r="J84" t="n">
         <v>9</v>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055331421</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Elisabeth Clausen</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>RWTH Aachen University</t>
@@ -3841,7 +3857,11 @@
       <c r="D85" t="n">
         <v>105</v>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Development and Evaluation of a UWB-Based Indoor Positioning System for Underground Mine Environments (2023)</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -3849,16 +3869,24 @@
       <c r="J85" t="n">
         <v>9</v>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5054432753</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Edna Hillmann</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Humboldt-Universität zu Berlin</t>
@@ -3872,7 +3900,11 @@
       <c r="D86" t="n">
         <v>130</v>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pinpointing pigs: performance and challenges of an ultra-wideband real-time location system for tracking growing-finishing pigs under practical conditions (2024)</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -3880,16 +3912,24 @@
       <c r="J86" t="n">
         <v>8</v>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5017297216</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Robert B. Kohlhaas</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Technische Universität Berlin (TU Berlin)</t>
@@ -3903,7 +3943,11 @@
       <c r="D87" t="n">
         <v>145</v>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Ultra-Wideband PIN-PD THz Emitter with &gt; 5.5 THz Bandwidth (2024)</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
@@ -3911,11 +3955,15 @@
       <c r="J87" t="n">
         <v>8</v>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5049029990</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3968,7 +3968,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Alexander Koelpin</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Universität Hamburg</t>
@@ -3982,7 +3986,11 @@
       <c r="D88" t="n">
         <v>193</v>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Heart Sound Detection Using an Ultra-Wideband FMCW Radar (2023)</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -3990,11 +3998,15 @@
       <c r="J88" t="n">
         <v>8</v>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5019989632</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4033,16 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Peter B. Shull</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Delft University of Technology</t>
@@ -4040,7 +4056,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>embedded systems/wireless communications/robotics/signal processing/AI hardware</t>
+          <t>Asynchronous Hyperbolic UWB Source-Localization and Self-Localization for Indoor Tracking and Navigation (2023)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -4048,16 +4064,24 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5076415123</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Yuchuan Du</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Eindhoven University of Technology</t>
@@ -4071,7 +4095,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>embedded systems/chip design/signal processing/IoT/electronics</t>
+          <t>Data-Driven Indoor Positioning Correction for Infrastructure-Enabled Autonomous Driving Systems: A Lifelong Framework (2023)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -4079,16 +4103,24 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004514343</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Yang Miao</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>University of Twente</t>
@@ -4102,7 +4134,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>localization/wireless sensing/embedded systems/robotics</t>
+          <t>A UAV-Aided Real-Time Channel Sounder for Highly Dynamic Nonstationary A2G Scenarios (2023)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4110,11 +4142,15 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039982512</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4155,7 +4155,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Luca Benini</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>ETH Zurich</t>
@@ -4167,22 +4171,34 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Self-Sustaining Ultrawideband Positioning System for Event-Driven Indoor Localization (2023)</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043408422</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Andreas Burg</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>EPFL</t>
@@ -4194,22 +4210,34 @@
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Single-Anchor UWB Localization Using Channel Impulse Response Distributions (2023)</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5059133771</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tülin Atmaca</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Institut Polytechnique de Paris</t>
@@ -4221,22 +4249,34 @@
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>XAI Empowered Dual Band Wi-Fi Based Indoor Localization via Ensemble Learning (2023)</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080399533</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Isaac Skog</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Grenoble INP</t>
@@ -4250,7 +4290,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>very strong in embedded systems and microelectronics.</t>
+          <t>MAINS: A Magnetic-Field-Aided Inertial Navigation System for Indoor Positioning (2024)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -4258,16 +4298,24 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057769293</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Xiang‐Gen Xia</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Harbin Institute of Technology</t>
@@ -4279,17 +4327,25 @@
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>An Adaptive IMU/UWB Fusion Method for NLOS Indoor Positioning and Navigation (2023)</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065367615</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4350,7 +4350,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kenji Suzuki</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>University of Tsukuba</t>
@@ -4362,22 +4366,34 @@
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Peer-to-Peer Ultra-Wideband Localization for Hands-Free Control of a Human-Guided Smart Stroller (2024)</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100618207</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Nobby Stevens</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>IMEC / KU Leuven</t>
@@ -4389,17 +4405,25 @@
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>An Experimental Testbed for the Performance Evaluation of Optical Time Difference of Arrival Based Indoor Positioning (2024)</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020679063</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4470,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Andreas Stöhr</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>University of Duisburg-Essen</t>
@@ -4464,8 +4492,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>www.uni-due.de/international/international-admissions-en.php#application
-https://www.uni-due.de/iw/en/</t>
+          <t>Ultra-Wideband Multi-Octave Planar Interconnect for Multi-Band THz Communications (2023)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4475,16 +4502,24 @@
       <c r="J102" t="n">
         <v>5</v>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5046865796</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ruediger Kays</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Technische Universität Dortmund</t>
@@ -4500,7 +4535,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>did not find phd</t>
+          <t>Achieving Sub-meter Accuracy for 5G Localization at FR1 Bandwidth Limitations (2023)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4510,16 +4545,24 @@
       <c r="J103" t="n">
         <v>6</v>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5032845767</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Monika Sester</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Leibniz University Hannover</t>
@@ -4535,7 +4578,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.uni-hannover.de/en/studium/vor-dem-studium/bewerbung-zulassung</t>
+          <t>Integrated Multi-Stereo Camera System for Robust Indoor Localization with Temporal Fusion (2024)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4545,11 +4588,15 @@
       <c r="J104" t="n">
         <v>7</v>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5020817045</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4601,7 +4601,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Daniel E. Rosner</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tampere University</t>
@@ -4617,7 +4621,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.tuni.fi/en/tau/doctoral-programmes/doctoral-programme-computing-and-electrical-engineering</t>
+          <t>FlexTDOA: Robust and Scalable Time-Difference of Arrival Localization Using Ultra-Wideband Devices (2023)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4627,16 +4631,24 @@
       <c r="J105" t="n">
         <v>7</v>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5082568352</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Mikko Vastaranta</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>University of Eastern Finland</t>
@@ -4652,7 +4664,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.uef.fi/en/degree-programme/doctoral-programme-in-science-forestry-and-technology</t>
+          <t>Ultra-Wideband-Based Method for Measuring Tree Positions With Decimeter-Level Accuracy Under a Forest Canopy (2025)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4662,16 +4674,24 @@
       <c r="J106" t="n">
         <v>6</v>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047838080</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Uwe D. Hanebeck</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Linköping University</t>
@@ -4687,7 +4707,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://liu.se/en/research/doctoral-studies/apply-for-doctoral-studies</t>
+          <t>Continuous-Time Ultra-Wideband-Inertial Fusion (2023)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -4697,16 +4717,24 @@
       <c r="J107" t="n">
         <v>8</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5055331421</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Naeem Khademi</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>University of Stavanger</t>
@@ -4724,8 +4752,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.uis.no/en/research/phd-at-uis
-https://www.uis.no/en/research/for-phd-candidates-tools-and-guidance</t>
+          <t>Evaluation Study of Inertial Positioning in Road Tunnels for Cooperative ITS Applications (2023)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -4735,16 +4762,24 @@
       <c r="J108" t="n">
         <v>5</v>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5113819740</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Johan Stien</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Vrije Universiteit Brussel</t>
@@ -4760,8 +4795,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.vub.be/en
-(did not find phD)</t>
+          <t>Machine learning-optimized terahertz ultra-wideband tunable metamaterial absorber (2025)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -4771,11 +4805,15 @@
       <c r="J109" t="n">
         <v>8</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5117422059</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4818,7 +4818,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Yang Miao</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>University of Twente</t>
@@ -4834,7 +4838,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://utwentecareers.nl/en/vacancies/?type=WP&amp;page=2&amp;category=PR</t>
+          <t>A UAV-Aided Real-Time Channel Sounder for Highly Dynamic Nonstationary A2G Scenarios (2023)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -4844,16 +4848,24 @@
       <c r="J110" t="n">
         <v>8</v>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5039982512</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Peter Brída</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Warsaw University of Technology</t>
@@ -4869,8 +4881,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.cwm.pw.edu.pl/en/International-students/Studies-in-English
-https://eng.pw.edu.pl/Academics/Faculties</t>
+          <t>Selection of Signal Sources Influence at Indoor Positioning System (2023)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -4880,16 +4891,24 @@
       <c r="J111" t="n">
         <v>6</v>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5089496860</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Suramate Chalermwisutkul</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Wrocław University of Science and Technology</t>
@@ -4907,7 +4926,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.polito.it/en/education/phd-programmes-and-postgraduate-school/admissions-to-phd-programmes/admissions/call-for-applications</t>
+          <t>Low-Cost Indoor Localization Using Dual-Chip RFID Tag (2024)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -4917,16 +4936,24 @@
       <c r="J112" t="n">
         <v>5</v>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5060445574</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Andrea Carena</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Politecnico di Torino</t>
@@ -4942,7 +4969,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.polito.it/en/education/phd-programmes-and-postgraduate-school/phd-programmes</t>
+          <t>ML-Based Spectral Power Profiles Prediction in Presence of ISRS for Ultra-Wideband Transmission (2023)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -4952,16 +4979,24 @@
       <c r="J113" t="n">
         <v>8</v>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5056219057</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Carlo Vallati</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>University of Pisa</t>
@@ -4977,7 +5012,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.unipi.it/en/education/courses/phd-programmes/</t>
+          <t>Short-Range Localization via Bluetooth Using Machine Learning Techniques for Industrial Production Monitoring (2023)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4987,11 +5022,15 @@
       <c r="J114" t="n">
         <v>7</v>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5086067526</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5035,7 +5035,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Isaac Skog</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Université Grenoble Alpes</t>
@@ -5051,7 +5055,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.univ-grenoble-alpes.fr/education/programs/programs-in-english/science-technology-health-engineering/science-technology-health-engineering-1372709.kjsp?RH=1580400124257</t>
+          <t>MAINS: A Magnetic-Field-Aided Inertial Navigation System for Indoor Positioning (2024)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5061,16 +5065,24 @@
       <c r="J115" t="n">
         <v>7</v>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5057769293</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Yuchuan Du</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Eindhoven University of Technology</t>
@@ -5086,7 +5098,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.tue.nl/en/education/graduate-school/phd</t>
+          <t>Data-Driven Indoor Positioning Correction for Infrastructure-Enabled Autonomous Driving Systems: A Lifelong Framework (2023)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5096,11 +5108,15 @@
       <c r="J116" t="n">
         <v>8</v>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5004514343</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5140,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tülin Atmaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Institut Polytechnique de Paris (3years phd programs)</t>
@@ -5140,7 +5160,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.ip-paris.fr/en/education/phd-programs</t>
+          <t>XAI Empowered Dual Band Wi-Fi Based Indoor Localization via Ensemble Learning (2023)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -5150,16 +5170,24 @@
       <c r="J118" t="n">
         <v>8</v>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5080399533</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Zijian Li</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Hong Kong University of Science and Technology</t>
@@ -5175,7 +5203,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://join.hkust.edu.hk/admissions/international-qualifications</t>
+          <t>FedPos: A Federated Transfer Learning Framework for CSI-Based Wi-Fi Indoor Positioning (2023)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -5185,11 +5213,15 @@
       <c r="J119" t="n">
         <v>9</v>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5038979005</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5256,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5261,7 +5261,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Xiang‐Gen Xia</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>City University of Hong Kong</t>
@@ -5277,7 +5281,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.cityu.edu.hk/en/admissions</t>
+          <t>An Adaptive IMU/UWB Fusion Method for NLOS Indoor Positioning and Navigation (2023)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -5287,16 +5291,24 @@
       <c r="J121" t="n">
         <v>9</v>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065367615</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Angela P. Schoellig</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>University of Toronto</t>
@@ -5312,7 +5324,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://future.utoronto.ca/international-students</t>
+          <t>UTIL: An ultra-wideband time-difference-of-arrival indoor localization dataset (2024)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -5322,16 +5334,24 @@
       <c r="J122" t="n">
         <v>8</v>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5052147335</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Shuguang Cui</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>University of British Columbia</t>
@@ -5347,8 +5367,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.grad.ubc.ca/prospective-students/international-students
-https://www.ubc.ca/admissions/</t>
+          <t>A Survey on Indoor Visible Light Positioning Systems: Fundamentals, Applications, and Challenges (2024)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -5358,16 +5377,24 @@
       <c r="J123" t="n">
         <v>8</v>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5009164482</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Xuemin Shen</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>University of Waterloo</t>
@@ -5383,7 +5410,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://uwaterloo.ca/future-students/financing/international-scholarships</t>
+          <t>A Survey of mmWave Radar-Based Sensing in Autonomous Vehicles, Smart Homes and Industry (2024)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -5393,16 +5420,24 @@
       <c r="J124" t="n">
         <v>7</v>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100773343</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jérôme Le Ny</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>McGill University</t>
@@ -5418,7 +5453,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.mcgill.ca/gradapplicants/how-apply</t>
+          <t>Calibration and Uncertainty Characterization for Ultra-Wideband Two-Way-Ranging Measurements (2023)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5428,11 +5463,15 @@
       <c r="J125" t="n">
         <v>8</v>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5012980200</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5476,7 +5476,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Andrew Chan</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>University of Alberta</t>
@@ -5490,7 +5494,11 @@
       <c r="D126" t="n">
         <v>94</v>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Automated Detection of In-Home Activities with Ultra-Wideband Sensors (2024)</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
@@ -5498,16 +5506,24 @@
       <c r="J126" t="n">
         <v>7</v>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043180508</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Zhengjun Yao</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>The University of Melbourne</t>
@@ -5521,7 +5537,11 @@
       <c r="D127" t="n">
         <v>19</v>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Multi‐Scale Dispersion Engineering on Biomass‐Derived Materials for Ultra‐Wideband and Wide‐Angle Microwave Absorption (2024)</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
@@ -5529,16 +5549,24 @@
       <c r="J127" t="n">
         <v>8</v>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5066063907</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bing Yu</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>UNSW Sydney</t>
@@ -5552,7 +5580,11 @@
       <c r="D128" t="n">
         <v>20</v>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Indoor Localization Methods for Smartphones with Multi-Source Sensors Fusion: Tasks, Challenges, Strategies, and Perspectives (2025)</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
@@ -5560,16 +5592,24 @@
       <c r="J128" t="n">
         <v>8</v>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5078494765</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Harry Kai-Ho Chan</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Monash University</t>
@@ -5583,7 +5623,11 @@
       <c r="D129" t="n">
         <v>36</v>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Contact Tracing Over Uncertain Indoor Positioning Data (2023)</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
@@ -5591,16 +5635,24 @@
       <c r="J129" t="n">
         <v>8</v>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5047655841</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Xiang‐Gen Xia</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Harbin Institute of Technology</t>
@@ -5616,7 +5668,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://en.hit.edu.cn/11959/list.htm</t>
+          <t>An Adaptive IMU/UWB Fusion Method for NLOS Indoor Positioning and Navigation (2023)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5626,11 +5678,15 @@
       <c r="J130" t="n">
         <v>7</v>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5065367615</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5691,7 +5691,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Kenji Suzuki</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>University of Tsukuba</t>
@@ -5707,8 +5711,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.tsukuba.ac.jp/en/admissions/financial-scholarships/
-https://www.tsukuba.ac.jp/en/admissions/guidebook-enrollment/</t>
+          <t>Peer-to-Peer Ultra-Wideband Localization for Hands-Free Control of a Human-Guided Smart Stroller (2024)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5718,11 +5721,15 @@
       <c r="J131" t="n">
         <v>7</v>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100618207</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6019,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Junming Zhao</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Arizona State University</t>
@@ -6020,22 +6031,34 @@
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>A Novel Ultra‐Wideband Electromagnetic‐Wave‐Absorbing Metastructure Inspired by Bionic Gyroid Structures (2023)</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5024794935</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Naofal Al‐Dhahir</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>University of Texas at Dallas</t>
@@ -6043,22 +6066,34 @@
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>OpenPose-Inspired Reduced-Complexity CSI-Based Wi-Fi Indoor Localization (2024)</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5081018704</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Wei Dong</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Northeastern University</t>
@@ -6066,22 +6101,34 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Asymmetry Stagger Array Structure Ultra-Wideband Vibration Harvester Integrating Magnetically Coupled Nonlinear Effects (2023)</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5110929783</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Mingzhe Chen</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>North Carolina State University</t>
@@ -6089,17 +6136,25 @@
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Complex-Valued Neural-Network-Based Federated Learning for Multiuser Indoor Positioning Performance Optimization (2024)</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5072241033</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,26 @@
           <t>Checked?</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Checked_General?</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Discovered_Field</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>General_PI</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>General_Paper</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -540,11 +560,35 @@
       <c r="J2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5043546527</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Pietro Manzoni</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>An evaluation methodology to determine the actual limitations of a TinyML-based solution (2023)</t>
         </is>
       </c>
     </row>
@@ -591,7 +635,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>they answered and told me to apply again for spring 2026</t>
+          <t>https://openalex.org/A5048811541</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -602,6 +646,26 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Christian Steger</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>TPDNet: A Tiny Pupil Detection Neural Network for Embedded Machine Learning Processor Arm Ethos-U55 (2024)</t>
         </is>
       </c>
     </row>
@@ -638,11 +702,35 @@
       <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100624451</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Xipeng Shen</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Space-Efficient TREC for Enabling Deep Learning on Microcontrollers (2023)</t>
         </is>
       </c>
     </row>
@@ -692,6 +780,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -728,11 +824,35 @@
       <c r="J6" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5048811541</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Christian Steger</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>TPDNet: A Tiny Pupil Detection Neural Network for Embedded Machine Learning Processor Arm Ethos-U55 (2024)</t>
         </is>
       </c>
     </row>
@@ -776,6 +896,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -821,6 +949,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -866,6 +1002,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -907,6 +1051,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,6 +1100,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -993,6 +1153,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1038,6 +1206,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1083,6 +1259,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1128,6 +1312,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1147,6 +1339,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1188,6 +1388,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1217,6 +1425,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1258,6 +1474,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1287,6 +1511,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1328,6 +1560,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1369,6 +1609,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1410,6 +1658,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1451,6 +1707,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1492,6 +1756,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1533,6 +1805,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1574,6 +1854,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1615,6 +1903,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1656,6 +1952,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1697,6 +2001,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1738,6 +2050,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1779,6 +2099,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1820,6 +2148,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1861,6 +2197,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1902,6 +2246,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1943,6 +2295,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1984,6 +2344,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2025,6 +2393,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2066,6 +2442,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2107,6 +2491,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2148,6 +2540,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2189,6 +2589,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2230,6 +2638,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2271,6 +2687,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2312,6 +2736,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2353,6 +2785,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2394,6 +2834,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2435,6 +2883,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -2464,6 +2920,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -2493,6 +2957,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -2522,6 +2994,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -2551,6 +3031,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2592,6 +3080,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2633,6 +3129,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2674,6 +3178,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2715,6 +3227,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2756,6 +3276,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2797,6 +3325,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2838,6 +3374,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2879,6 +3423,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2920,6 +3472,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2961,6 +3521,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -2990,6 +3558,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3031,6 +3607,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3072,6 +3656,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3113,6 +3705,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3154,6 +3754,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3195,6 +3803,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3236,6 +3852,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3277,6 +3901,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3318,6 +3950,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3359,6 +3999,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3400,6 +4048,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -3429,6 +4085,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3470,6 +4134,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3511,6 +4183,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3552,6 +4232,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3593,6 +4281,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3634,6 +4330,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3677,6 +4381,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3720,6 +4432,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3763,6 +4483,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -3794,6 +4522,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3837,6 +4573,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3880,6 +4624,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3923,6 +4675,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3966,6 +4726,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4009,6 +4777,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -4036,6 +4812,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4075,6 +4859,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4114,6 +4906,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4153,6 +4953,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4192,6 +5000,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4231,6 +5047,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4270,6 +5094,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4309,6 +5141,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4348,6 +5188,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4387,6 +5235,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4426,6 +5282,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -4445,6 +5309,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4468,6 +5340,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4513,6 +5393,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4556,6 +5444,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4599,6 +5495,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4642,6 +5546,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4685,6 +5597,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4728,6 +5648,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4773,6 +5701,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4816,6 +5752,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4859,6 +5803,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4902,6 +5854,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4947,6 +5907,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4990,6 +5958,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5033,6 +6009,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5076,6 +6060,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5119,6 +6111,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -5138,6 +6138,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5181,6 +6189,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5224,6 +6240,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -5259,6 +6283,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5302,6 +6334,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5345,6 +6385,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5388,6 +6436,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5431,6 +6487,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5474,6 +6538,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5517,6 +6589,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5560,6 +6640,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5603,6 +6691,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5646,6 +6742,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5689,6 +6793,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5732,6 +6844,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -5751,6 +6871,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -5770,6 +6898,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -5789,6 +6925,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -5808,6 +6952,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -5827,6 +6979,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -5846,6 +7006,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -5865,6 +7033,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -5884,6 +7060,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -5903,6 +7087,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -5922,6 +7114,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -5941,6 +7141,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -5960,6 +7168,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -5979,6 +7195,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -5998,6 +7222,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -6017,6 +7249,14 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6052,6 +7292,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6087,6 +7335,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6122,6 +7378,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6157,6 +7421,14 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1044,7 +1044,11 @@
       <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5060233962</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
@@ -1053,12 +1057,24 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Acoustic Signals</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tero Koivisto</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Generating Synthetic Mechanocardiograms for Machine Learning-Based Peak Detection (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1102,7 +1118,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5044609448</t>
+          <t>https://openalex.org/A5116007457</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1171,12 +1171,24 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Guanghan Wu</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>When the Code Autopilot Breaks: Why Large Language Models Falter in Embedded Machine Learning (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1213,7 +1225,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5043408422</t>
+          <t>https://openalex.org/A5038717922</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1224,12 +1236,24 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Francesco Conti</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>RedMule: A mixed-precision matrix–matrix operation engine for flexible and energy-efficient on-chip linear algebra and TinyML training acceleration (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1266,7 +1290,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5089609880</t>
+          <t>https://openalex.org/A5022006569</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1277,12 +1301,24 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Shoshanna Saxe</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Machine Learning-Augmented Optimization of Large Bilevel and Two-stage Stochastic Programs: Application to Cycling Network Design (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1319,7 +1355,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5049439078</t>
+          <t>https://openalex.org/A5060229356</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1330,12 +1366,24 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Deepu Jose</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Test and Evaluation of Systems with Embedded Machine Learning Components (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1395,7 +1443,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5089609880</t>
+          <t>https://openalex.org/A5022006569</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1406,12 +1454,24 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Shoshanna Saxe</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Machine Learning-Augmented Optimization of Large Bilevel and Two-stage Stochastic Programs: Application to Cycling Network Design (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5089609880</t>
+          <t>https://openalex.org/A5087192549</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1552,12 +1552,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tee Hui Teo</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>An Embedded Machine Learning Fault Detection System for Electric Fan Drive (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1589,7 +1601,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -1627,7 +1639,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5045152528</t>
+          <t>https://openalex.org/A5016730248</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1638,12 +1650,24 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Vision &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Harsha De Silva</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Clinicopathological concordance of clinicians, Chat-GPT4 and ORAD for odontogenic keratocysts and tumours referred to a single New Zealand Centre- A 15-year retrospective study. (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1676,7 +1700,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5046856721</t>
+          <t>https://openalex.org/A5082835974</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1687,12 +1711,24 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tegawendé François Bissyandé</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>An empirical study of AI techniques in mobile applications (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5087987207</t>
+          <t>https://openalex.org/A5041954621</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1772,12 +1772,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Akimasa Hirata</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Roadmap towards personalized approaches and safety considerations in non-ionizing radiation: from dosimetry to therapeutic and diagnostic applications (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1810,7 +1822,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5102935450</t>
+          <t>https://openalex.org/A5089388923</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1821,12 +1833,24 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Masato Motomura</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Pianissimo: A Sub-mW Class DNN Accelerator With Progressively Adjustable Bit-Precision (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1859,7 +1883,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5008352007</t>
+          <t>https://openalex.org/A5054498473</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1870,12 +1894,24 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Keisuke Morishima</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Feedback control of automatic navigation for cyborg cockroach without external motion capture system (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1908,7 +1944,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5020830042</t>
+          <t>https://openalex.org/A5121246706</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1919,12 +1955,24 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kazunori OHNO</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>AI-IoT-Robotics Integration: Survey of Frameworks, Emerging Trends, and the Path Toward Connected Robotics (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1957,7 +2005,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5045353484</t>
+          <t>https://openalex.org/A5016969134</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1968,12 +2016,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ao Guo</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Challenges and Emerging Issues for Generative AI and Hyper Intelligence (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5102856248</t>
+          <t>https://openalex.org/A5089388923</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2077,12 +2077,24 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Masato Motomura</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Pianissimo: A Sub-mW Class DNN Accelerator With Progressively Adjustable Bit-Precision (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2115,7 +2127,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5073445963</t>
+          <t>https://openalex.org/A5052749873</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2126,12 +2138,24 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mohamed M. Kamra</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Systematic Review on AI-Powered UAVs: The Role of Artificial Intelligence in UAV Evolution and Applications Expansion (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2164,7 +2188,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5020400844</t>
+          <t>https://openalex.org/A5016969134</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2175,12 +2199,24 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ao Guo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Challenges and Emerging Issues for Generative AI and Hyper Intelligence (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2213,7 +2249,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5027367677</t>
+          <t>https://openalex.org/A5041549339</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2224,12 +2260,24 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hiroki Matsutani</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Addressing the Gap Between Training Data and Deployed Environment by On-Device Learning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2262,7 +2310,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100654317</t>
+          <t>https://openalex.org/A5082399620</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2273,12 +2321,24 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yeunwoong Kyung</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>TinyML-Based Classification in an ECG Monitoring Embedded System (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2371,7 +2371,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100657256</t>
+          <t>https://openalex.org/A5033521909</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2382,12 +2382,24 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hee‐Woong Kim</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Enhanced Anomaly Detection in Manufacturing Processes Through Hybrid Deep Learning Techniques (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2420,7 +2432,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5009725517</t>
+          <t>https://openalex.org/A5011213078</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2431,12 +2443,24 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ashok Kumar Das</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A Contextual Aware Enhanced LoRaWAN Adaptive Data Rate for mobile IoT applications (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2469,7 +2493,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100713090</t>
+          <t>https://openalex.org/A5088838086</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2480,12 +2504,24 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Vision &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hyunbo Cho</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Automated Footwear Surface Inspection System Based on the Deep Learning Object Detection (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2518,7 +2554,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5009184228</t>
+          <t>https://openalex.org/A5063908850</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2529,12 +2565,24 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jong Hwan Ko</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>An Efficient Ventricular Arrhythmias Detection on Microcontrollers with Optimized 1D CNN (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2567,7 +2615,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5081367261</t>
+          <t>https://openalex.org/A5021420311</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2578,12 +2626,24 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Acoustic Signals</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sung Ho Cho</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Machine Learning for Healthcare Radars: Recent Progresses in Human Vital Sign Measurement and Activity Recognition (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5044783058</t>
+          <t>https://openalex.org/A5100658136</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2687,12 +2687,24 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Seulki Lee</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>MicroDeblur: Image Motion Deblurring on Microcontroller-based Vision Systems (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2725,7 +2737,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5080533010</t>
+          <t>https://openalex.org/A5082399620</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2736,12 +2748,24 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Yeunwoong Kyung</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>TinyML-Based Classification in an ECG Monitoring Embedded System (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2774,7 +2798,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5033053320</t>
+          <t>https://openalex.org/A5100657575</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2785,12 +2809,24 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Shaobo Zhang</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>A Quality-Aware and Obfuscation-Based Data Collection Scheme for Cyber-Physical Metaverse Systems (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2823,7 +2859,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5126346057</t>
+          <t>https://openalex.org/A5062886480</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2834,12 +2870,24 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ru Huang</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>A Model-Specific End-to-End Design Methodology for Resource-Constrained TinyML Hardware (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2872,7 +2920,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5061103594</t>
+          <t>https://openalex.org/A5005913897</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2883,12 +2931,24 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Yonina C. Eldar</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Physics-Embedded Machine Learning for Electromagnetic Data Imaging: Examining three types of data-driven imaging methods (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5061028507</t>
+          <t>https://openalex.org/A5034020559</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2992,12 +2992,24 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jian Min Xiong</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Machine learning for mechanical design of composite materials and composite structures (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3030,7 +3042,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5026515323</t>
+          <t>https://openalex.org/A5100777770</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3041,12 +3053,24 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hua Wei</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CityFlowER: An Efficient and Realistic Traffic Simulator with Embedded Machine Learning Models (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3079,7 +3103,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5110977361</t>
+          <t>https://openalex.org/A5069094261</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3090,12 +3114,24 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Zhenhong Du</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Satellite-Based Global Sea Surface Oxygen Mapping and Interpretation with Spatiotemporal Machine Learning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3128,7 +3164,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5024794935</t>
+          <t>https://openalex.org/A5103045425</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3139,12 +3175,24 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lijia Pan</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>AI-Enabled Flexible Sensing Ecosystems for Parkinson’s Disease: Advancing Digital Biomarkers and Closed-Loop Interventions (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3177,7 +3225,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5026515323</t>
+          <t>https://openalex.org/A5036767358</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3188,12 +3236,24 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sensor Fusion &amp; DAQ</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ting Han</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>A novel multi-graph-structure guided human lower-limb physiological load estimation method based on multi-inertial-sensors fusion during walking (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3286,7 +3286,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5022499594</t>
+          <t>https://openalex.org/A5069094261</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3297,12 +3297,24 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Zhenhong Du</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Satellite-Based Global Sea Surface Oxygen Mapping and Interpretation with Spatiotemporal Machine Learning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3325,7 +3337,11 @@
       <c r="J49" t="n">
         <v>10</v>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5103045425</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
@@ -3334,12 +3350,24 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lijia Pan</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>AI-Enabled Flexible Sensing Ecosystems for Parkinson’s Disease: Advancing Digital Biomarkers and Closed-Loop Interventions (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3362,7 +3390,11 @@
       <c r="J50" t="n">
         <v>9</v>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5075307304</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
@@ -3371,12 +3403,24 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>YongAn Huang</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>A Flexible, Large-Scale Sensing Array with Low-Power In-Sensor Intelligence (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3399,7 +3443,11 @@
       <c r="J51" t="n">
         <v>9</v>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5108044017</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
@@ -3408,12 +3456,24 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Zhihan Lv</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>TinyML-Driven Distributed Collaborative Computing for Autonomous Vehicle Groups in Open Scenes (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3436,7 +3496,11 @@
       <c r="J52" t="n">
         <v>9</v>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100673818</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
@@ -3445,12 +3509,24 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Liangpei Zhang</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>An optimized semi-empirical physical approach for satellite-based PM 2.5 retrieval: embedding machine learning to simulate complex physical parameters (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3570,7 +3570,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -3804,7 +3804,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5037337156</t>
+          <t>https://openalex.org/A5068445964</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3815,12 +3815,24 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Haytham H. Elmousalami</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>AI-Powered Digital Twins and Internet of Things for Smart Cities and Sustainable Building Environment (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3853,7 +3865,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5087753687</t>
+          <t>https://openalex.org/A5087058987</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3864,12 +3876,24 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Vision &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ricardo da Silva Torres</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Identifying losers: Automatic identification of growth-stunted salmon in aquaculture using computer vision (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3902,7 +3926,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5020679063</t>
+          <t>https://openalex.org/A5000635267</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3913,12 +3937,24 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vijay Janapa Reddi</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>TinyML4D: Scaling Embedded Machine Learning Education in the Developing World (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3951,7 +3987,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5026442244</t>
+          <t>https://openalex.org/A5047378679</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3962,12 +3998,24 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Jeroen Famaey</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Towards energy-aware tinyML on battery-less IoT devices (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4000,7 +4048,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5033726877</t>
+          <t>https://openalex.org/A5076386475</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -4011,12 +4059,24 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tomás Norton</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>How AI Improves Sustainable Chicken Farming: A Literature Review of Welfare, Economic, and Environmental Dimensions (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4108,7 +4108,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5004224779</t>
+          <t>https://openalex.org/A5035616620</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4157,12 +4157,24 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Pieter Meyns</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Gait Stride Length Estimation Using Embedded Machine Learning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4195,7 +4207,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5117422059</t>
+          <t>https://openalex.org/A5078788396</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4206,12 +4218,24 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bruno da Silva</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Secure Tiny Machine Learning on Edge Devices: A Lightweight Dual Attestation Mechanism for Machine Learning (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4244,7 +4268,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5000544440</t>
+          <t>https://openalex.org/A5084189456</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4255,12 +4279,24 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Guillaume Drion</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Improving the Performance and Learning Stability of Parallelizable RNNs Designed for Ultra-Low Power Applications (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4293,7 +4329,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5073439066</t>
+          <t>https://openalex.org/A5006928330</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4304,12 +4340,24 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Johan Ruuskanen</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Extending Microservice Model Validity using Universal Differential Equations (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4390,7 +4390,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5004012289</t>
+          <t>https://openalex.org/A5025956807</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4401,12 +4401,24 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Jaya Prakash Champati</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>The Case for Hierarchical Deep Learning Inference at the Network Edge (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4439,7 +4451,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5057769293</t>
+          <t>https://openalex.org/A5020214726</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4450,12 +4462,24 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stefanos Kaxiras</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Efficient CNN Inference on Ultra-Low-Power MCUs via Saturation-Aware Convolution (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4488,7 +4512,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5087753687</t>
+          <t>https://openalex.org/A5060398288</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4499,12 +4523,24 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sara Modarres Razavi</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Guest Editorial: SPECIAL ISSUE ON TinyML for Edge-Driven 6G Networks (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4537,7 +4573,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5054197935</t>
+          <t>https://openalex.org/A5018279980</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4548,12 +4584,24 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Olaf Landsiedel</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>LightEQ: On-Device Earthquake Detection with Embedded Machine Learning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4586,7 +4634,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5078102195</t>
+          <t>https://openalex.org/A5000688587</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4597,12 +4645,24 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Daniel Strüber</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Cross-platform edge deployment of machine learning models: a model-driven approach (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4695,7 +4695,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5078102195</t>
+          <t>https://openalex.org/A5000688587</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4706,12 +4706,24 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Daniel Strüber</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Cross-platform edge deployment of machine learning models: a model-driven approach (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4743,7 +4755,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
@@ -4781,7 +4793,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5056278281</t>
+          <t>https://openalex.org/A5087728544</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4792,12 +4804,24 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Martin Andraud</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Hardware-efficient tractable probabilistic inference for TinyML Neurosymbolic AI applications (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4830,7 +4854,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5044609448</t>
+          <t>https://openalex.org/A5116007457</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4841,12 +4865,24 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Guanghan Wu</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>When the Code Autopilot Breaks: Why Large Language Models Falter in Embedded Machine Learning (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4879,7 +4915,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5029534229</t>
+          <t>https://openalex.org/A5034968363</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4890,12 +4926,24 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Onel L. Alcaraz López</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>TinyML: Tools, applications, challenges, and future research directions (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -4976,7 +4976,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5093561961</t>
+          <t>https://openalex.org/A5075314597</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4987,12 +4987,24 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Juha Plosila</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>JCCO: Jointly Optimizing the Computational and Communication Costs for Resource Allocation in Energy-Efficient Swarm Robotics (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5025,7 +5037,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5101480038</t>
+          <t>https://openalex.org/A5113331842</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -5036,12 +5048,24 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Pedro H. J. Nardelli</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Edge AI System for EV Trip Analytics: On-Device WLTP Class 3B Processing and Battery Temperature Prediction (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5076,7 +5100,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5052147335</t>
+          <t>https://openalex.org/A5000635267</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5087,12 +5111,24 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Vijay Janapa Reddi</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>TinyML4D: Scaling Embedded Machine Learning Education in the Developing World (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5127,7 +5163,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5046027378</t>
+          <t>https://openalex.org/A5012747021</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5138,12 +5174,24 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Christian Heumann</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Knowledge-embedded machine learning for production optimization on logistical delivery grids (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5178,7 +5226,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5035297149</t>
+          <t>https://openalex.org/A5014251134</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5189,12 +5237,24 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Holger Fröning</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Beyond Noise: Understanding and Overcoming Temperature Effects in Analog DNN Inference (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5288,7 +5288,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5055331421</t>
+          <t>https://openalex.org/A5063508488</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5339,12 +5339,24 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Jörg Henkel</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Hardware–Software Co-design for Ultra-Resource-Constrained Embedded Machine Learning Inference: A Printed Electronics Use Case (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5379,7 +5391,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5054432753</t>
+          <t>https://openalex.org/A5046956677</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5390,12 +5402,24 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Wolfgang Ecker</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Exploring Hardware-Efficient Architectures of Golomb–Rice Decoder for TinyML Applications (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5428,11 +5452,7 @@
       <c r="J86" t="n">
         <v>8</v>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>https://openalex.org/A5017297216</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
@@ -5441,12 +5461,24 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gergana Vladova</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Contesting Openness in AI. Reflections on the transformative value and participatory potential of open source AI (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5481,7 +5513,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5049029990</t>
+          <t>https://openalex.org/A5064915684</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5492,12 +5524,24 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Felix Archibald Enge</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Embedded machine learning as an enabler of lean construction (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5576,7 +5576,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5019989632</t>
+          <t>https://openalex.org/A5103184703</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5587,12 +5587,24 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stefan Wolff</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>The Multi-Stage Mixed Methods Framework: A new research design to combine hypothesis development and hypothesis testing and to embed machine learning and practitioner engagement in the social sciences (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -5622,7 +5634,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
@@ -5658,7 +5670,7 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5076415123</t>
+          <t>https://openalex.org/A5081295372</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5669,12 +5681,24 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Marco Antonio Zúñiga</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>SolarML: Optimizing Sensing and Inference for Solar-Powered TinyML Platforms (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5705,7 +5729,7 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5004514343</t>
+          <t>https://openalex.org/A5009986948</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5716,12 +5740,24 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Alessandro Pozzebon</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Sleep Posture Detection via Embedded Machine Learning on a Reduced Set of Pressure Sensors (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5752,7 +5788,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5039982512</t>
+          <t>https://openalex.org/A5000417436</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5763,12 +5799,24 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Jian-Jia Chen</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Register Your Forests: Decision Tree Ensemble Optimization by Explicit CPU Register Allocation (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -5858,12 +5858,24 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Luca Benini</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Work in Progress: Linear Transformers for TinyML (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5894,7 +5906,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5059133771</t>
+          <t>https://openalex.org/A5074236306</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5905,12 +5917,24 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>David Atienza</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>BiomedBench: A Benchmark Suite of TinyML Biomedical Applications for Low-Power Wearables (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5941,7 +5965,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5080399533</t>
+          <t>https://openalex.org/A5046851981</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5952,12 +5976,24 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Enzo Tartaglione</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Shannon Strikes Again! Entropy-based Pruning in Deep Neural Networks for Transfer Learning under Extreme Memory and Computation Budgets (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5988,7 +6024,7 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5057769293</t>
+          <t>https://openalex.org/A5011273650</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5999,12 +6035,24 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Pascal Xavier</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Tiny, Distributed, and Eco-Optimized: Proposal of Design Guidelines for Environmentally Friendly ML Devices (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6035,7 +6083,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5065367615</t>
+          <t>https://openalex.org/A5101671535</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6046,12 +6094,24 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Dechun Li</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>A TinyML System for Early Screening of CHD on ESP32 (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -6142,7 +6142,7 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100618207</t>
+          <t>https://openalex.org/A5005578675</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6153,12 +6153,24 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Vision &amp; Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Marcus Völp</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Multi-version Machine Learning and Rejuvenation for Resilient Perception in Safety-critical Systems (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6189,7 +6201,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5020679063</t>
+          <t>https://openalex.org/A5000635267</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -6200,12 +6212,24 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Vijay Janapa Reddi</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>TinyML4D: Scaling Embedded Machine Learning Education in the Developing World (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -6300,7 +6324,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5046865796</t>
+          <t>https://openalex.org/A5059943616</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6311,12 +6335,24 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Anton Grabmaier</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Semi-Supervised Anomaly Detection in the TinyML Domain Through Multi-Target Few-Shot Domain Adaptation (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6351,7 +6387,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5032845767</t>
+          <t>https://openalex.org/A5000417436</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6362,12 +6398,24 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Jian-Jia Chen</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Robust and Tiny Binary Neural Networks using Gradient-based Explainability Methods (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6402,7 +6450,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5020817045</t>
+          <t>https://openalex.org/A5035792471</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6413,12 +6461,24 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Soumyajyoti Maji</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Continuous Freezing of Gait Detection With TinyML on Embedded Systems (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -6513,7 +6513,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5082568352</t>
+          <t>https://openalex.org/A5127700274</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6524,12 +6524,24 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Jere Piirainen</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Objektintunnistuksen optimointi resurssirajoitteisissa mikrokontrollereissa: TinyML:n ja FOMO-algoritmin hyödyntäminen sulautetuissa sovelluksissa (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6564,7 +6576,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5047838080</t>
+          <t>https://openalex.org/A5123574880</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6575,12 +6587,24 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Salman Khalil</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Potential of TinyML and Federated Reinforcement Learning-Based Trajectory Optimization in Space-Air-Ground Integrated Network (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6615,7 +6639,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5055331421</t>
+          <t>https://openalex.org/A5018537955</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6626,12 +6650,24 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Eduardo de la Torre</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Dynamically reconfigurable variable-precision sparse-dense matrix acceleration in Tensorflow Lite (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6668,7 +6704,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5113819740</t>
+          <t>https://openalex.org/A5045380393</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6679,12 +6715,24 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ferhat Karaca</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Facilitating Circular Economy Strategies Using Digital Construction Tools: Framework Development (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6719,7 +6767,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5117422059</t>
+          <t>https://openalex.org/A5078788396</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6730,12 +6778,24 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Bruno da Silva</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Secure Tiny Machine Learning on Edge Devices: A Lightweight Dual Attestation Mechanism for Machine Learning (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -6830,7 +6830,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5039982512</t>
+          <t>https://openalex.org/A5000417436</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6841,12 +6841,24 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Jian-Jia Chen</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Register Your Forests: Decision Tree Ensemble Optimization by Explicit CPU Register Allocation (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6881,7 +6893,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5089496860</t>
+          <t>https://openalex.org/A5053781299</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6892,12 +6904,24 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Marcin Paprzycki</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Frugal Heart Rate Correction Method for Scalable Health and Safety Monitoring in Construction Sites (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6934,7 +6958,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5060445574</t>
+          <t>https://openalex.org/A5027153286</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6945,12 +6969,24 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Krzysztof M. Walkowiak</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>A Novel One-Versus-All Approach for Multiclass Classification in TinyML Systems (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6985,7 +7021,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5056219057</t>
+          <t>https://openalex.org/A5012150553</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6996,12 +7032,24 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Marian Verhelst</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>HTVM: Efficient Neural Network Deployment On Heterogeneous TinyML Platforms (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7036,7 +7084,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5086067526</t>
+          <t>https://openalex.org/A5102026679</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -7047,12 +7095,24 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Qinghe Zheng</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Advancements in TinyML: Applications, Limitations, and Impact on IoT Devices (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -7147,7 +7147,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5057769293</t>
+          <t>https://openalex.org/A5011273650</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -7158,12 +7158,24 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Pascal Xavier</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Tiny, Distributed, and Eco-Optimized: Proposal of Design Guidelines for Environmentally Friendly ML Devices (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7198,7 +7210,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5004514343</t>
+          <t>https://openalex.org/A5009986948</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -7209,12 +7221,24 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Alessandro Pozzebon</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Sleep Posture Detection via Embedded Machine Learning on a Reduced Set of Pressure Sensors (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -7276,7 +7300,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5080399533</t>
+          <t>https://openalex.org/A5046851981</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7287,12 +7311,24 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Enzo Tartaglione</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Shannon Strikes Again! Entropy-based Pruning in Deep Neural Networks for Transfer Learning under Extreme Memory and Computation Budgets (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7327,7 +7363,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5038979005</t>
+          <t>https://openalex.org/A5014819244</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7338,12 +7374,24 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Yangdi Lyu</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Microprocessor Design Space Exploration via Space Partitioning and Bayesian Optimization (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -7381,7 +7429,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="O120" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5065367615</t>
+          <t>https://openalex.org/A5100419083</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7480,12 +7480,24 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Zhenjiang Li</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>DTMM: Deploying TinyML Models on Extremely Weak IoT Devices with Pruning (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7520,7 +7532,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5052147335</t>
+          <t>https://openalex.org/A5022006569</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7531,12 +7543,24 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Shoshanna Saxe</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Machine Learning–Augmented Optimization of Large Bilevel and Two-Stage Stochastic Programs: Application to Cycling Network Design (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7571,7 +7595,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5009164482</t>
+          <t>https://openalex.org/A5013246362</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7582,12 +7606,24 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Steven J. E. Wilton</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>DEBUG-HD: Debugging TinyML models on-device using Hyper-Dimensional computing (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7622,7 +7658,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100773343</t>
+          <t>https://openalex.org/A5080711681</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7633,12 +7669,24 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Ghulam Muhammad</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>A multi-resolution fusion approach for human activity recognition from video data in tiny edge devices (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7673,7 +7721,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5012980200</t>
+          <t>https://openalex.org/A5034701871</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7684,12 +7732,24 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Brett H. Meyer</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Zero-Shot NAS for TinyML Semantic Segmentation via Weight Sharing (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -7784,7 +7784,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5043180508</t>
+          <t>https://openalex.org/A5003799782</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7795,12 +7795,24 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Witold Pedrycz</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Guest Editorial of the Special section on Lightweight Large Model for Edge Computing in Consumer Devices (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7835,7 +7847,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5066063907</t>
+          <t>https://openalex.org/A5044922102</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7846,12 +7858,24 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Elaine Wong</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>TinyML-Empowered Human-to-Machine Applications over Future Access Networks (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7886,7 +7910,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5078494765</t>
+          <t>https://openalex.org/A5080202547</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7897,12 +7921,24 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Nadeem Ahmed</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Intelligence at the Extreme Edge: A Survey on Reformable TinyML (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7937,7 +7973,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5047655841</t>
+          <t>https://openalex.org/A5029767607</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7948,12 +7984,24 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Maryam Shojaei Baghini</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Embedded Machine Learning on Accelerometer Data for Exercise Classification (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7988,7 +8036,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5065367615</t>
+          <t>https://openalex.org/A5101671535</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7999,12 +8047,24 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Dechun Li</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>A TinyML System for Early Screening of CHD on ESP32 (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -8099,7 +8099,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5100618207</t>
+          <t>https://openalex.org/A5041549339</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -8110,12 +8110,24 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Hiroki Matsutani</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>InstantFT: A Field-Programmable Gate Array-Based Runtime Subsecond Fine-Tuning of Convolutional Neural Network Models (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -8547,7 +8559,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5024794935</t>
+          <t>https://openalex.org/A5074371899</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8558,12 +8570,24 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Andreas Spanias</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Real-time PV Fault Detection using Embedded Machine Learning (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8590,7 +8614,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5081018704</t>
+          <t>https://openalex.org/A5051431139</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8601,12 +8625,24 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Tooraj Nikoubin</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>TinyML Enabled Real-Time Bearing Fault Classification in Motors Using Vibration Signals (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8633,7 +8669,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5110929783</t>
+          <t>https://openalex.org/A5143702357</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8644,12 +8680,24 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Jiaming Hao</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>TinyML Model for Anomalous Gait Recognition in Real Clinical Scenarios: A Study on Generalization (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8676,7 +8724,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://openalex.org/A5072241033</t>
+          <t>https://openalex.org/A5065410886</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -8687,12 +8735,24 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Ranga Raju Vatsavai</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Efficient Multi-Domain Instance Segmentation with Modular Shared-Head Routing (2025)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
